--- a/artfynd/A 55487-2019 artfynd.xlsx
+++ b/artfynd/A 55487-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55487-2019 artfynd.xlsx
+++ b/artfynd/A 55487-2019 artfynd.xlsx
@@ -1041,11 +1041,11 @@
         <v>80774228</v>
       </c>
       <c r="B5" t="n">
-        <v>56411</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ej möjlig att validera</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>528725.8049133548</v>
+        <v>528726</v>
       </c>
       <c r="R5" t="n">
-        <v>6609262.146746515</v>
+        <v>6609262</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,19 +1127,9 @@
           <t>2019-10-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-10-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
